--- a/output/yearly_total_coral_cover_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_26_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.2576742142835</v>
+        <v>1.257310967632929</v>
       </c>
       <c r="C3" t="n">
-        <v>4.669316654416432</v>
+        <v>4.702303377279124</v>
       </c>
       <c r="D3" t="n">
-        <v>6.173499638857251</v>
+        <v>6.107536010608908</v>
       </c>
       <c r="E3" t="n">
-        <v>12.10049050755718</v>
+        <v>12.06715035552096</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.3838422263916</v>
+        <v>1.387676740515436</v>
       </c>
       <c r="C4" t="n">
-        <v>5.226772249155535</v>
+        <v>5.315542255252836</v>
       </c>
       <c r="D4" t="n">
-        <v>6.408184325897118</v>
+        <v>6.33638978664758</v>
       </c>
       <c r="E4" t="n">
-        <v>13.01879880144425</v>
+        <v>13.03960878241585</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.554279977877129</v>
+        <v>1.560074883850024</v>
       </c>
       <c r="C5" t="n">
-        <v>5.955820399713848</v>
+        <v>6.116124822064693</v>
       </c>
       <c r="D5" t="n">
-        <v>6.702578436579136</v>
+        <v>6.640836869673336</v>
       </c>
       <c r="E5" t="n">
-        <v>14.21267881417011</v>
+        <v>14.31703657558805</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.754396871619849</v>
+        <v>1.755341421670708</v>
       </c>
       <c r="C6" t="n">
-        <v>6.824863889893072</v>
+        <v>7.070871089404957</v>
       </c>
       <c r="D6" t="n">
-        <v>7.01180752313462</v>
+        <v>7.084668447068993</v>
       </c>
       <c r="E6" t="n">
-        <v>15.59106828464754</v>
+        <v>15.91088095814466</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.995445672450351</v>
+        <v>1.9676286736979</v>
       </c>
       <c r="C7" t="n">
-        <v>7.839578236362431</v>
+        <v>8.138383891877444</v>
       </c>
       <c r="D7" t="n">
-        <v>7.410923565427091</v>
+        <v>7.503150855159338</v>
       </c>
       <c r="E7" t="n">
-        <v>17.24594747423987</v>
+        <v>17.60916342073468</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.245133642535392</v>
+        <v>1.175704481014589</v>
       </c>
       <c r="C8" t="n">
-        <v>5.414884225040261</v>
+        <v>5.688892469298759</v>
       </c>
       <c r="D8" t="n">
-        <v>5.681743784986164</v>
+        <v>5.830726476052085</v>
       </c>
       <c r="E8" t="n">
-        <v>12.34176165256182</v>
+        <v>12.69532342636543</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.577327761325631</v>
+        <v>1.443531756932484</v>
       </c>
       <c r="C9" t="n">
-        <v>6.617445933475574</v>
+        <v>7.000794774487256</v>
       </c>
       <c r="D9" t="n">
-        <v>6.218934483529014</v>
+        <v>6.433593502988046</v>
       </c>
       <c r="E9" t="n">
-        <v>14.41370817833022</v>
+        <v>14.87792003440779</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.918646076005498</v>
+        <v>1.721319407697868</v>
       </c>
       <c r="C10" t="n">
-        <v>7.95443686934784</v>
+        <v>8.517598855302127</v>
       </c>
       <c r="D10" t="n">
-        <v>6.771733388609455</v>
+        <v>6.965178544600218</v>
       </c>
       <c r="E10" t="n">
-        <v>16.64481633396279</v>
+        <v>17.20409680760021</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.268094740840507</v>
+        <v>2.009842751145114</v>
       </c>
       <c r="C11" t="n">
-        <v>9.362354582867049</v>
+        <v>10.16522613178932</v>
       </c>
       <c r="D11" t="n">
-        <v>7.302948572162103</v>
+        <v>7.515680226102075</v>
       </c>
       <c r="E11" t="n">
-        <v>18.93339789586966</v>
+        <v>19.69074910903651</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.61401732224249</v>
+        <v>2.287620571784426</v>
       </c>
       <c r="C12" t="n">
-        <v>10.83396913484443</v>
+        <v>11.94481897217383</v>
       </c>
       <c r="D12" t="n">
-        <v>7.8445661362506</v>
+        <v>8.089437943828692</v>
       </c>
       <c r="E12" t="n">
-        <v>21.29255259333753</v>
+        <v>22.32187748778694</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.936195813280924</v>
+        <v>2.539879294624714</v>
       </c>
       <c r="C13" t="n">
-        <v>12.31418596560619</v>
+        <v>13.73920311282575</v>
       </c>
       <c r="D13" t="n">
-        <v>8.317848215982597</v>
+        <v>8.586046114548461</v>
       </c>
       <c r="E13" t="n">
-        <v>23.56822999486971</v>
+        <v>24.86512852199893</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.678474414996687</v>
+        <v>1.46349130272072</v>
       </c>
       <c r="C14" t="n">
-        <v>8.662912289842728</v>
+        <v>9.647624872156362</v>
       </c>
       <c r="D14" t="n">
-        <v>6.319500154759676</v>
+        <v>6.524430170544155</v>
       </c>
       <c r="E14" t="n">
-        <v>16.66088685959909</v>
+        <v>17.63554634542124</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.713856602257742</v>
+        <v>1.474015638110246</v>
       </c>
       <c r="C15" t="n">
-        <v>9.202873527178472</v>
+        <v>10.49649302463337</v>
       </c>
       <c r="D15" t="n">
-        <v>6.348766053823272</v>
+        <v>6.559085864504069</v>
       </c>
       <c r="E15" t="n">
-        <v>17.26549618325949</v>
+        <v>18.52959452724768</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.000438574604428</v>
+        <v>1.679672147195868</v>
       </c>
       <c r="C16" t="n">
-        <v>10.74538570261402</v>
+        <v>12.3970191353766</v>
       </c>
       <c r="D16" t="n">
-        <v>6.807301136568788</v>
+        <v>7.084232528982729</v>
       </c>
       <c r="E16" t="n">
-        <v>19.55312541378724</v>
+        <v>21.1609238115552</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.619147401229052</v>
+        <v>1.327097094169711</v>
       </c>
       <c r="C17" t="n">
-        <v>9.766583241479948</v>
+        <v>11.36052917914098</v>
       </c>
       <c r="D17" t="n">
-        <v>6.31756611178231</v>
+        <v>6.575834480338519</v>
       </c>
       <c r="E17" t="n">
-        <v>17.70329675449131</v>
+        <v>19.26346075364921</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.860775146198277</v>
+        <v>1.485001394920768</v>
       </c>
       <c r="C18" t="n">
-        <v>11.31882453666458</v>
+        <v>13.18309470468998</v>
       </c>
       <c r="D18" t="n">
-        <v>6.743340273637109</v>
+        <v>7.033859054277825</v>
       </c>
       <c r="E18" t="n">
-        <v>19.92293995649997</v>
+        <v>21.70195515388857</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.879389082670797</v>
+        <v>1.46217576079703</v>
       </c>
       <c r="C19" t="n">
-        <v>12.02012619171625</v>
+        <v>14.00668285378263</v>
       </c>
       <c r="D19" t="n">
-        <v>6.85742917434763</v>
+        <v>7.139426384915485</v>
       </c>
       <c r="E19" t="n">
-        <v>20.75694444873468</v>
+        <v>22.60828499949514</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.11166077201855</v>
+        <v>1.597490046873367</v>
       </c>
       <c r="C20" t="n">
-        <v>13.76878575008954</v>
+        <v>15.99848204858968</v>
       </c>
       <c r="D20" t="n">
-        <v>7.32942401811837</v>
+        <v>7.572769821570026</v>
       </c>
       <c r="E20" t="n">
-        <v>23.20987054022646</v>
+        <v>25.16874191703308</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.263754732291707</v>
+        <v>0.9342212978842225</v>
       </c>
       <c r="C21" t="n">
-        <v>10.12249623670055</v>
+        <v>11.66340816337817</v>
       </c>
       <c r="D21" t="n">
-        <v>6.121785984601411</v>
+        <v>6.334952863624522</v>
       </c>
       <c r="E21" t="n">
-        <v>17.50803695359366</v>
+        <v>18.93258232488692</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_26_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257310967632929</v>
+        <v>1.282649875879539</v>
       </c>
       <c r="C3" t="n">
-        <v>4.702303377279124</v>
+        <v>4.66366178763997</v>
       </c>
       <c r="D3" t="n">
-        <v>6.107536010608908</v>
+        <v>6.081863308142854</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06715035552096</v>
+        <v>12.02817497166236</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.387676740515436</v>
+        <v>1.456680640618577</v>
       </c>
       <c r="C4" t="n">
-        <v>5.315542255252836</v>
+        <v>5.217971825492625</v>
       </c>
       <c r="D4" t="n">
-        <v>6.33638978664758</v>
+        <v>6.267147905943367</v>
       </c>
       <c r="E4" t="n">
-        <v>13.03960878241585</v>
+        <v>12.94180037205457</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.560074883850024</v>
+        <v>1.681641414445468</v>
       </c>
       <c r="C5" t="n">
-        <v>6.116124822064693</v>
+        <v>5.946016107290369</v>
       </c>
       <c r="D5" t="n">
-        <v>6.640836869673336</v>
+        <v>6.565355797074784</v>
       </c>
       <c r="E5" t="n">
-        <v>14.31703657558805</v>
+        <v>14.19301331881062</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.755341421670708</v>
+        <v>1.923979518043156</v>
       </c>
       <c r="C6" t="n">
-        <v>7.070871089404957</v>
+        <v>6.873594250626235</v>
       </c>
       <c r="D6" t="n">
-        <v>7.084668447068993</v>
+        <v>6.966106054499859</v>
       </c>
       <c r="E6" t="n">
-        <v>15.91088095814466</v>
+        <v>15.76367982316925</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.9676286736979</v>
+        <v>2.188322629664659</v>
       </c>
       <c r="C7" t="n">
-        <v>8.138383891877444</v>
+        <v>8.004618495759905</v>
       </c>
       <c r="D7" t="n">
-        <v>7.503150855159338</v>
+        <v>7.358597347203396</v>
       </c>
       <c r="E7" t="n">
-        <v>17.60916342073468</v>
+        <v>17.55153847262796</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.175704481014589</v>
+        <v>1.358847629183032</v>
       </c>
       <c r="C8" t="n">
-        <v>5.688892469298759</v>
+        <v>5.763521974189924</v>
       </c>
       <c r="D8" t="n">
-        <v>5.830726476052085</v>
+        <v>5.546288443652427</v>
       </c>
       <c r="E8" t="n">
-        <v>12.69532342636543</v>
+        <v>12.66865804702538</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.443531756932484</v>
+        <v>1.692612296080295</v>
       </c>
       <c r="C9" t="n">
-        <v>7.000794774487256</v>
+        <v>7.253240442388999</v>
       </c>
       <c r="D9" t="n">
-        <v>6.433593502988046</v>
+        <v>5.962326149345963</v>
       </c>
       <c r="E9" t="n">
-        <v>14.87792003440779</v>
+        <v>14.90817888781526</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.721319407697868</v>
+        <v>2.028890753074741</v>
       </c>
       <c r="C10" t="n">
-        <v>8.517598855302127</v>
+        <v>8.940462623977991</v>
       </c>
       <c r="D10" t="n">
-        <v>6.965178544600218</v>
+        <v>6.35024580005388</v>
       </c>
       <c r="E10" t="n">
-        <v>17.20409680760021</v>
+        <v>17.31959917710661</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.009842751145114</v>
+        <v>2.379088823735816</v>
       </c>
       <c r="C11" t="n">
-        <v>10.16522613178932</v>
+        <v>10.71378296611459</v>
       </c>
       <c r="D11" t="n">
-        <v>7.515680226102075</v>
+        <v>6.80521980851622</v>
       </c>
       <c r="E11" t="n">
-        <v>19.69074910903651</v>
+        <v>19.89809159836663</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.287620571784426</v>
+        <v>2.709659691077563</v>
       </c>
       <c r="C12" t="n">
-        <v>11.94481897217383</v>
+        <v>12.51002072692763</v>
       </c>
       <c r="D12" t="n">
-        <v>8.089437943828692</v>
+        <v>7.247537702974885</v>
       </c>
       <c r="E12" t="n">
-        <v>22.32187748778694</v>
+        <v>22.46721812098008</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.539879294624714</v>
+        <v>3.03488146661269</v>
       </c>
       <c r="C13" t="n">
-        <v>13.73920311282575</v>
+        <v>14.28053729794906</v>
       </c>
       <c r="D13" t="n">
-        <v>8.586046114548461</v>
+        <v>7.6381552955275</v>
       </c>
       <c r="E13" t="n">
-        <v>24.86512852199893</v>
+        <v>24.95357406008925</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.46349130272072</v>
+        <v>1.753470122124101</v>
       </c>
       <c r="C14" t="n">
-        <v>9.647624872156362</v>
+        <v>9.824948142497423</v>
       </c>
       <c r="D14" t="n">
-        <v>6.524430170544155</v>
+        <v>5.790269419831348</v>
       </c>
       <c r="E14" t="n">
-        <v>17.63554634542124</v>
+        <v>17.36868768445287</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.474015638110246</v>
+        <v>1.80211572086953</v>
       </c>
       <c r="C15" t="n">
-        <v>10.49649302463337</v>
+        <v>10.59813336445404</v>
       </c>
       <c r="D15" t="n">
-        <v>6.559085864504069</v>
+        <v>5.747092155798573</v>
       </c>
       <c r="E15" t="n">
-        <v>18.52959452724768</v>
+        <v>18.14734124112214</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.679672147195868</v>
+        <v>2.09066118862471</v>
       </c>
       <c r="C16" t="n">
-        <v>12.3970191353766</v>
+        <v>12.43186136140032</v>
       </c>
       <c r="D16" t="n">
-        <v>7.084232528982729</v>
+        <v>6.11725031020779</v>
       </c>
       <c r="E16" t="n">
-        <v>21.1609238115552</v>
+        <v>20.63977286023282</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.327097094169711</v>
+        <v>1.676245847708046</v>
       </c>
       <c r="C17" t="n">
-        <v>11.36052917914098</v>
+        <v>11.34212140968636</v>
       </c>
       <c r="D17" t="n">
-        <v>6.575834480338519</v>
+        <v>5.63132446651379</v>
       </c>
       <c r="E17" t="n">
-        <v>19.26346075364921</v>
+        <v>18.64969172390819</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.485001394920768</v>
+        <v>1.915890462314693</v>
       </c>
       <c r="C18" t="n">
-        <v>13.18309470468998</v>
+        <v>13.15325939195792</v>
       </c>
       <c r="D18" t="n">
-        <v>7.033859054277825</v>
+        <v>5.946838543704628</v>
       </c>
       <c r="E18" t="n">
-        <v>21.70195515388857</v>
+        <v>21.01598839797724</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.46217576079703</v>
+        <v>1.922360179685679</v>
       </c>
       <c r="C19" t="n">
-        <v>14.00668285378263</v>
+        <v>13.99516695321181</v>
       </c>
       <c r="D19" t="n">
-        <v>7.139426384915485</v>
+        <v>5.972128364566028</v>
       </c>
       <c r="E19" t="n">
-        <v>22.60828499949514</v>
+        <v>21.88965549746352</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.597490046873367</v>
+        <v>2.135576146094002</v>
       </c>
       <c r="C20" t="n">
-        <v>15.99848204858968</v>
+        <v>16.00766138962439</v>
       </c>
       <c r="D20" t="n">
-        <v>7.572769821570026</v>
+        <v>6.336189865731871</v>
       </c>
       <c r="E20" t="n">
-        <v>25.16874191703308</v>
+        <v>24.47942740145027</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9342212978842225</v>
+        <v>1.268162779483775</v>
       </c>
       <c r="C21" t="n">
-        <v>11.66340816337817</v>
+        <v>11.67043747694058</v>
       </c>
       <c r="D21" t="n">
-        <v>6.334952863624522</v>
+        <v>5.255050023907113</v>
       </c>
       <c r="E21" t="n">
-        <v>18.93258232488692</v>
+        <v>18.19365028033146</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_26_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.282649875879539</v>
+        <v>2.587169794454022</v>
       </c>
       <c r="C3" t="n">
-        <v>4.66366178763997</v>
+        <v>7.756010199924201</v>
       </c>
       <c r="D3" t="n">
-        <v>6.081863308142854</v>
+        <v>8.216313064238275</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02817497166236</v>
+        <v>18.5594930586165</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.456680640618577</v>
+        <v>1.057581133308666</v>
       </c>
       <c r="C4" t="n">
-        <v>5.217971825492625</v>
+        <v>4.602743066270651</v>
       </c>
       <c r="D4" t="n">
-        <v>6.267147905943367</v>
+        <v>5.820359548227099</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94180037205457</v>
+        <v>11.48068374780642</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.681641414445468</v>
+        <v>1.131242892186448</v>
       </c>
       <c r="C5" t="n">
-        <v>5.946016107290369</v>
+        <v>5.336067218115224</v>
       </c>
       <c r="D5" t="n">
-        <v>6.565355797074784</v>
+        <v>6.200177331585332</v>
       </c>
       <c r="E5" t="n">
-        <v>14.19301331881062</v>
+        <v>12.667487441887</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.923979518043156</v>
+        <v>1.207029790446432</v>
       </c>
       <c r="C6" t="n">
-        <v>6.873594250626235</v>
+        <v>6.26614803361772</v>
       </c>
       <c r="D6" t="n">
-        <v>6.966106054499859</v>
+        <v>6.575009885684636</v>
       </c>
       <c r="E6" t="n">
-        <v>15.76367982316925</v>
+        <v>14.04818770974879</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.188322629664659</v>
+        <v>1.294525914523502</v>
       </c>
       <c r="C7" t="n">
-        <v>8.004618495759905</v>
+        <v>7.325204001060102</v>
       </c>
       <c r="D7" t="n">
-        <v>7.358597347203396</v>
+        <v>7.041013570402865</v>
       </c>
       <c r="E7" t="n">
-        <v>17.55153847262796</v>
+        <v>15.66074348598647</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.358847629183032</v>
+        <v>1.386142560536007</v>
       </c>
       <c r="C8" t="n">
-        <v>5.763521974189924</v>
+        <v>8.525773170339498</v>
       </c>
       <c r="D8" t="n">
-        <v>5.546288443652427</v>
+        <v>7.488188137968867</v>
       </c>
       <c r="E8" t="n">
-        <v>12.66865804702538</v>
+        <v>17.40010386884437</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.692612296080295</v>
+        <v>1.471668549382278</v>
       </c>
       <c r="C9" t="n">
-        <v>7.253240442388999</v>
+        <v>9.860185797237785</v>
       </c>
       <c r="D9" t="n">
-        <v>5.962326149345963</v>
+        <v>7.907405185282037</v>
       </c>
       <c r="E9" t="n">
-        <v>14.90817888781526</v>
+        <v>19.2392595319021</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.028890753074741</v>
+        <v>0.9413291512629692</v>
       </c>
       <c r="C10" t="n">
-        <v>8.940462623977991</v>
+        <v>7.205223116054105</v>
       </c>
       <c r="D10" t="n">
-        <v>6.35024580005388</v>
+        <v>6.230642170048298</v>
       </c>
       <c r="E10" t="n">
-        <v>17.31959917710661</v>
+        <v>14.37719443736537</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.379088823735816</v>
+        <v>0.8617290474026379</v>
       </c>
       <c r="C11" t="n">
-        <v>10.71378296611459</v>
+        <v>7.692464501671798</v>
       </c>
       <c r="D11" t="n">
-        <v>6.80521980851622</v>
+        <v>6.116209657641289</v>
       </c>
       <c r="E11" t="n">
-        <v>19.89809159836663</v>
+        <v>14.67040320671572</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.709659691077563</v>
+        <v>0.9125737610055801</v>
       </c>
       <c r="C12" t="n">
-        <v>12.51002072692763</v>
+        <v>9.111031029446185</v>
       </c>
       <c r="D12" t="n">
-        <v>7.247537702974885</v>
+        <v>6.555404310613142</v>
       </c>
       <c r="E12" t="n">
-        <v>22.46721812098008</v>
+        <v>16.5790091010649</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.03488146661269</v>
+        <v>0.7106184407649688</v>
       </c>
       <c r="C13" t="n">
-        <v>14.28053729794906</v>
+        <v>8.663727140437253</v>
       </c>
       <c r="D13" t="n">
-        <v>7.6381552955275</v>
+        <v>6.009709666684595</v>
       </c>
       <c r="E13" t="n">
-        <v>24.95357406008925</v>
+        <v>15.38405524788682</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.753470122124101</v>
+        <v>0.7546400078233958</v>
       </c>
       <c r="C14" t="n">
-        <v>9.824948142497423</v>
+        <v>10.13420848681221</v>
       </c>
       <c r="D14" t="n">
-        <v>5.790269419831348</v>
+        <v>6.38833048630442</v>
       </c>
       <c r="E14" t="n">
-        <v>17.36868768445287</v>
+        <v>17.27717898094003</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.80211572086953</v>
+        <v>0.7210347839070275</v>
       </c>
       <c r="C15" t="n">
-        <v>10.59813336445404</v>
+        <v>10.92153087570998</v>
       </c>
       <c r="D15" t="n">
-        <v>5.747092155798573</v>
+        <v>6.457131365418037</v>
       </c>
       <c r="E15" t="n">
-        <v>18.14734124112214</v>
+        <v>18.09969702503505</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.09066118862471</v>
+        <v>0.7818835066162448</v>
       </c>
       <c r="C16" t="n">
-        <v>12.43186136140032</v>
+        <v>12.69086604073471</v>
       </c>
       <c r="D16" t="n">
-        <v>6.11725031020779</v>
+        <v>6.890523889457791</v>
       </c>
       <c r="E16" t="n">
-        <v>20.63977286023282</v>
+        <v>20.36327343680875</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.676245847708046</v>
+        <v>0.4709541912042375</v>
       </c>
       <c r="C17" t="n">
-        <v>11.34212140968636</v>
+        <v>9.459090043032807</v>
       </c>
       <c r="D17" t="n">
-        <v>5.63132446651379</v>
+        <v>5.740092294667294</v>
       </c>
       <c r="E17" t="n">
-        <v>18.64969172390819</v>
+        <v>15.67013652890434</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.915890462314693</v>
+        <v>0.3635804447907637</v>
       </c>
       <c r="C18" t="n">
-        <v>13.15325939195792</v>
+        <v>8.339927112622568</v>
       </c>
       <c r="D18" t="n">
-        <v>5.946838543704628</v>
+        <v>5.246096484844384</v>
       </c>
       <c r="E18" t="n">
-        <v>21.01598839797724</v>
+        <v>13.94960404225772</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.922360179685679</v>
+        <v>0.4223969497521903</v>
       </c>
       <c r="C19" t="n">
-        <v>13.99516695321181</v>
+        <v>10.25194948898253</v>
       </c>
       <c r="D19" t="n">
-        <v>5.972128364566028</v>
+        <v>5.743744396127092</v>
       </c>
       <c r="E19" t="n">
-        <v>21.88965549746352</v>
+        <v>16.41809083486181</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.135576146094002</v>
+        <v>0.4794168564148449</v>
       </c>
       <c r="C20" t="n">
-        <v>16.00766138962439</v>
+        <v>12.27125725446258</v>
       </c>
       <c r="D20" t="n">
-        <v>6.336189865731871</v>
+        <v>6.271492692022008</v>
       </c>
       <c r="E20" t="n">
-        <v>24.47942740145027</v>
+        <v>19.02216680289943</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.268162779483775</v>
+        <v>0.5307328089158259</v>
       </c>
       <c r="C21" t="n">
-        <v>11.67043747694058</v>
+        <v>14.27810664157574</v>
       </c>
       <c r="D21" t="n">
-        <v>5.255050023907113</v>
+        <v>6.73308101012773</v>
       </c>
       <c r="E21" t="n">
-        <v>18.19365028033146</v>
+        <v>21.5419204606193</v>
       </c>
     </row>
   </sheetData>
